--- a/productos_template.xlsx
+++ b/productos_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Laravel\Laravel-React\E-Aqua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CA3FA0-23DB-4CD5-B119-2E0A62F3A5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD39AE2-52F7-4DF1-8E29-148AFA77F33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="147">
   <si>
     <t>category_name</t>
   </si>
@@ -436,9 +436,6 @@
     <t>Difusores 215mm</t>
   </si>
   <si>
-    <t>940/Bolsa</t>
-  </si>
-  <si>
     <t>https://res.cloudinary.com/dnbklbswg/image/upload/v1779108718/3.KrakenBombaSumergible2_xozkii.png</t>
   </si>
   <si>
@@ -461,6 +458,9 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dnbklbswg/image/upload/v1779108719/7.BolsaCarriersBiol%C3%B3gicos_bwuu7n.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dnbklbswg/image/upload/v1779108719/2.MiltonRoy_BombaDosificadora_y2kv39.png</t>
   </si>
 </sst>
 </file>
@@ -570,7 +570,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -587,8 +587,14 @@
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -954,7 +960,7 @@
         <v>130</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="8">
+      <c r="D2" s="12">
         <v>3750</v>
       </c>
       <c r="E2" s="2">
@@ -978,7 +984,7 @@
         <v>131</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="9">
+      <c r="D3" s="13">
         <v>13500</v>
       </c>
       <c r="E3" s="2">
@@ -989,7 +995,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="7" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1002,7 +1008,7 @@
         <v>132</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="8">
+      <c r="D4" s="12">
         <v>5850</v>
       </c>
       <c r="E4" s="2">
@@ -1013,10 +1019,10 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="L4" s="2"/>
     </row>
@@ -1028,7 +1034,7 @@
         <v>133</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="9">
+      <c r="D5" s="13">
         <v>55500</v>
       </c>
       <c r="E5" s="2">
@@ -1039,7 +1045,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -1052,7 +1058,7 @@
         <v>134</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="8">
+      <c r="D6" s="12">
         <v>2090</v>
       </c>
       <c r="E6" s="2">
@@ -1063,7 +1069,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1076,7 +1082,7 @@
         <v>135</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="9">
+      <c r="D7" s="13">
         <v>5750</v>
       </c>
       <c r="E7" s="2">
@@ -1087,7 +1093,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1100,8 +1106,8 @@
         <v>136</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="8" t="s">
-        <v>138</v>
+      <c r="D8" s="8">
+        <v>940</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1111,10 +1117,10 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L8" s="2"/>
     </row>
@@ -1137,7 +1143,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -2663,15 +2669,15 @@
     <hyperlink ref="J63" r:id="rId63" xr:uid="{E358B1A4-8E22-4C38-B8EA-B1E9B432C637}"/>
     <hyperlink ref="J64" r:id="rId64" xr:uid="{B245FE4D-AF44-41AA-B323-41E4D5544C18}"/>
     <hyperlink ref="J2" r:id="rId65" xr:uid="{6BD91CDE-FB48-4EE8-B564-20813000D2E5}"/>
-    <hyperlink ref="J3" r:id="rId66" xr:uid="{01992AD4-C26F-47AA-A3C2-00C35639C316}"/>
-    <hyperlink ref="J4" r:id="rId67" xr:uid="{BA08CC2F-2514-48AA-9417-2A097568A641}"/>
-    <hyperlink ref="K4" r:id="rId68" xr:uid="{103A0283-8E4F-4A51-97B8-0441CC00BCC9}"/>
-    <hyperlink ref="J5" r:id="rId69" xr:uid="{C9C9A4C9-7B09-41B6-B903-0C45635E0209}"/>
-    <hyperlink ref="J6" r:id="rId70" xr:uid="{5EC39D3B-DAD4-4504-B068-6C5CB9358BEA}"/>
-    <hyperlink ref="J7" r:id="rId71" xr:uid="{39A62845-F077-45B4-9E4A-2A23D6007F74}"/>
-    <hyperlink ref="J8" r:id="rId72" xr:uid="{A2863B25-63AA-4B65-83D1-A437CF493653}"/>
-    <hyperlink ref="J9" r:id="rId73" xr:uid="{020102F8-DA46-484F-94EB-FDAD083BCF22}"/>
-    <hyperlink ref="K8" r:id="rId74" xr:uid="{4299EF44-97FA-458D-9E94-4B93FE15E56F}"/>
+    <hyperlink ref="J4" r:id="rId66" xr:uid="{BA08CC2F-2514-48AA-9417-2A097568A641}"/>
+    <hyperlink ref="K4" r:id="rId67" xr:uid="{103A0283-8E4F-4A51-97B8-0441CC00BCC9}"/>
+    <hyperlink ref="J5" r:id="rId68" xr:uid="{C9C9A4C9-7B09-41B6-B903-0C45635E0209}"/>
+    <hyperlink ref="J6" r:id="rId69" xr:uid="{5EC39D3B-DAD4-4504-B068-6C5CB9358BEA}"/>
+    <hyperlink ref="J7" r:id="rId70" xr:uid="{39A62845-F077-45B4-9E4A-2A23D6007F74}"/>
+    <hyperlink ref="J8" r:id="rId71" xr:uid="{A2863B25-63AA-4B65-83D1-A437CF493653}"/>
+    <hyperlink ref="J9" r:id="rId72" xr:uid="{020102F8-DA46-484F-94EB-FDAD083BCF22}"/>
+    <hyperlink ref="K8" r:id="rId73" xr:uid="{4299EF44-97FA-458D-9E94-4B93FE15E56F}"/>
+    <hyperlink ref="J3" r:id="rId74" xr:uid="{5B8D55CC-210C-4FF0-9F34-5A8FE02474E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
